--- a/CO_top75_ECE_contacts.xlsx
+++ b/CO_top75_ECE_contacts.xlsx
@@ -806,16 +806,24 @@
           <t>4700 S. Yosemite St., Greenwood Village, CO 80111</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Director of Extended Child Services</t>
+          <t>Interim Superintendent</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>sconley@cherrycreekschools.org</t>
+          <t>jperry@cherrycreekschools.org</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -825,7 +833,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>720-554-4100</t>
+          <t>303-773-1184</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr"/>
@@ -833,12 +841,12 @@
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>https://www.cherrycreekschools.org/departments</t>
+          <t>https://www.cherrycreekschools.org/about-us/superintendent</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Email found in secondary source; first name not confirmed. Verify full name of Director of Extended Child Services.</t>
+          <t>Christopher Smith resigned January 30, 2026; Jennifer Perry serving as Interim Superintendent as of February 2, 2026. ECE contact: sconley@cherrycreekschools.org (Director of Extended Child Services, full name not confirmed).</t>
         </is>
       </c>
     </row>
@@ -1014,14 +1022,22 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>395 S. Pratt Pkwy., Longmont, CO 80501</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+          <t>1050 North Main St., Longmont, CO 80501</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Jackie</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Kapushion</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Director of Early Childhood Education</t>
+          <t>Superintendent</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1036,7 +1052,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>303-702-8371</t>
+          <t>303-776-6200</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr"/>
@@ -1048,12 +1064,12 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>https://www.svvsd.org/departments/early-childhood/</t>
+          <t>https://www.svvsd.org/about/superintendent/</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Department email found; individual director name not confirmed publicly. Recommend Apollo.io enrichment.</t>
+          <t>Jackie Kapushion is new Superintendent effective July 1, 2025. Email shown is ECE dept inbox (earlychildhood@svvsd.org); Jackie's personal email not found. ECE Director name not confirmed — recommend Apollo.io enrichment.</t>
         </is>
       </c>
     </row>
@@ -1379,26 +1395,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>18551 E. 160th Ave., Brighton, CO 80601</t>
+          <t>88 N. 40th Avenue, Building A, Brighton, CO 80601</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Bethany</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Ager</t>
+          <t>Pierce</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Preschool Curriculum Coordinator</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>wpierce@sd27j.net</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>303-655-2900</t>
@@ -1413,12 +1437,12 @@
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>https://www.sd27j.org/departments/early-childhood</t>
+          <t>https://www.sd27j.org/about-us/leadership</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Creative Curriculum adoption documented. Email needed — check Apollo.io.</t>
+          <t>Creative Curriculum adoption documented. ECE contact: Bethany Ager, Early Childhood Education Coordinator &amp; Director (email not found — check Apollo.io).</t>
         </is>
       </c>
     </row>
@@ -1453,24 +1477,32 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Tuck</t>
+          <t>Gaal</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Early Childhood Coordinator</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>michael.gaal@d11.org</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>719-520-2542</t>
+          <t>719-520-2001</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr"/>
@@ -1478,12 +1510,12 @@
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://www.d11.org/departments/early-childhood</t>
+          <t>https://www.d11.org/administration/superintendent</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>Phone confirmed. Email needed — check Apollo.io. Email format likely susan.tuck@d11.org.</t>
+          <t>ECE contact: Susan Tuck, Early Childhood Coordinator (phone 719-520-2542; email likely susan.tuck@d11.org — verify via Apollo.io).</t>
         </is>
       </c>
     </row>
@@ -1518,24 +1550,32 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Deirdre</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Wagner</t>
+          <t>Pilch</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>ECE Program Representative</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>dpilch@greeleyschools.org</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>970-348-6000</t>
+          <t>970-348-6012</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr"/>
@@ -1543,12 +1583,12 @@
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>https://www.greeleyschools.org/departments/early-childhood</t>
+          <t>https://www.greeleyschools.org/our-district/our-leadership-team/superintendent</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Phone confirmed. Email needed — check Apollo.io.</t>
+          <t>ECE contact: Beth Wagner, ECE Program Representative (email not found — likely advisory role; check Apollo.io for ECE Director).</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1653,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>Phone confirmed. Email needed — check Apollo.io. Likely kdonathan@d51schools.org.</t>
+          <t>ECE Director identified; email not found — likely kdonathan@d51schools.org (check Apollo.io). Superintendent: Brian Hill (970-254-5100).</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2310,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>CDE SchoolView reports 10 schools, 7,590 students. Relatively large for rural Arapahoe County. No dedicated ECE Director found; superintendent listed.</t>
+          <t>CDE SchoolView reports 10 schools, 7,590 students. No dedicated ECE Director found; superintendent listed.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2448,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>Name confirmed; email needed — check Apollo.io. Likely mbrom@lewispalmer.org.</t>
+          <t>Curriculum Director identified; email not confirmed — likely mbrom@lewispalmer.org (check Apollo.io). Superintendent: Amber Whetstine (719-481-9546).</t>
         </is>
       </c>
     </row>
@@ -2510,11 +2550,27 @@
           <t>930 Colorado Ave., Montrose, CO 81401</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Carrie</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Stephenson</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>970-249-7726</t>
@@ -2529,12 +2585,12 @@
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>https://www.montrose.k12.co.us</t>
+          <t>https://www.mcsd.org/district_directory/superintendent</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>Teaching Strategies GOLD used for kindergarten readiness assessment. ECE director name not confirmed; email needed — check Apollo.io.</t>
+          <t>Teaching Strategies GOLD used for kindergarten readiness assessment. Superintendent email format: c***@mcsd.org — verify via Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2654,12 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>https://www.rfsd.k12.co.us/departments/early-childhood</t>
+          <t>https://www.rfsd.k12.co.us/en-US/senior-leadership-team-a1e1ad59</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>Name confirmed; new role as of Fall 2024. Email needed — check Apollo.io. Likely amelnick@rfsd.k12.co.us.</t>
+          <t>Adele Melnick, Director ECE / Basalt ECE Center (new role Fall 2024). Email not found — likely a.melnick@rfschools.com (check Apollo.io). Superintendent: Anna Cole (970-384-6000).</t>
         </is>
       </c>
     </row>
@@ -2636,11 +2692,27 @@
           <t>4750 E. 96th Ave., Commerce City, CO 80022</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Loría</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>720-685-7700</t>
@@ -2655,12 +2727,12 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>https://www.adams14.org</t>
+          <t>https://www.adams14.org/about/superintendent</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Superintendent email format: k******@adams14.org — verify via Apollo.io. No ECE Director identified publicly.</t>
         </is>
       </c>
     </row>
@@ -2762,14 +2834,34 @@
           <t>1765 Meeker St., Delta, CO 81416</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>G.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Pope</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>gpope@deltacounty.com</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>970-874-4438</t>
+          <t>970-874-2188</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr"/>
@@ -2777,12 +2869,12 @@
       <c r="O35" s="4" t="inlineStr"/>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>https://www.deltaschools.com</t>
+          <t>https://www.deltaschools.com/en-US/superintendent-corner-ecbab8ca</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>No ECE director identified publicly. Superintendent listed as primary contact.</t>
         </is>
       </c>
     </row>
@@ -2890,21 +2982,29 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>David</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Peak</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Preschool Coordinator</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr"/>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>dpeak@cmsd12.org</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>719-475-6100</t>
@@ -2915,12 +3015,12 @@
       <c r="O37" s="4" t="inlineStr"/>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>https://www.cmsd12.org</t>
+          <t>https://www.cmsd12.org/page/meet-our-superintendent</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>Name confirmed; email needed — check Apollo.io. Likely mgordon@cmsd12.org.</t>
+          <t>ECE contact: Matthew Gordon, Preschool Coordinator (email not found — likely mgordon@cmsd12.org; check Apollo.io).</t>
         </is>
       </c>
     </row>
@@ -2953,9 +3053,21 @@
           <t>PO Box 7, Frisco, CO 80443</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Byrd</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr">
@@ -2972,12 +3084,12 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>https://www.summitk12.org</t>
+          <t>https://www.summitk12.org/superintendent</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>Strong buying signal — preschool at capacity. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Strong buying signal — preschool at capacity. Superintendent email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3010,9 +3122,21 @@
           <t>715 W. Platte Ave., Fort Morgan, CO 80701</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Sanders</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr">
@@ -3025,12 +3149,12 @@
       <c r="O39" s="4" t="inlineStr"/>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>https://www.fmre3.org</t>
+          <t>https://www.fortmorgank12.com/departments/superintendent</t>
         </is>
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Superintendent email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3063,11 +3187,31 @@
           <t>101 N. 14th St., Canon City, CO 81212</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Hartman</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>adam.hartman@canoncityschools.org</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t>719-276-5700</t>
@@ -3078,12 +3222,12 @@
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>https://www.canoncityschools.org</t>
+          <t>https://www.canoncityschools.org/departments/superintendent</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>No ECE director identified publicly. Superintendent listed as primary contact.</t>
         </is>
       </c>
     </row>
@@ -3116,14 +3260,34 @@
           <t>644 N. Ponderosa Dr., Elizabeth, CO 80107</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Snowberger</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>dsnowberger@esdk12.org</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>303-646-1596</t>
+          <t>303-646-1836</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr"/>
@@ -3131,12 +3295,12 @@
       <c r="O41" s="4" t="inlineStr"/>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>https://www.elizabeth.k12.co.us</t>
+          <t>https://www.elizabethschooldistrict.org/departments/superintendents-office/our-superintendent</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Appointed March 2023; 37+ years education experience.</t>
         </is>
       </c>
     </row>
@@ -3169,11 +3333,27 @@
           <t>620 Birch St., Keenesburg, CO 80643</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Rabenhorst</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
           <t>303-732-4420</t>
@@ -3189,7 +3369,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Superintendent confirmed (High confidence). Email not retrieved — check Apollo.io or district website directly.</t>
         </is>
       </c>
     </row>
@@ -3299,11 +3479,27 @@
           <t>107 Mountain Dr., Fort Lupton, CO 80621</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Ralston</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
           <t>303-857-7070</t>
@@ -3323,7 +3519,7 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>Strong buying signal — new ECE facility. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Strong buying signal — new ECE facility opened 2024. Justin Ralston, Ed.D., Superintendent (High confidence). Email not retrieved — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3356,9 +3552,21 @@
           <t>400 N. Elm St., Cortez, CO 81321</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr">
@@ -3376,7 +3584,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Eddie Ramirez is new Superintendent as of January 2026. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3409,9 +3617,21 @@
           <t>800 N. Boulevard, Gunnison, CO 81230</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Leslie</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Nichols</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="inlineStr">
@@ -3429,7 +3649,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Leslie Nichols is retiring June 30, 2026. New superintendent search likely underway — verify status before outreach. Email not found.</t>
         </is>
       </c>
     </row>
@@ -3462,9 +3682,21 @@
           <t>209 Victoria Ave., Alamosa, CO 81101</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr">
@@ -3482,7 +3714,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Diana Jones, Superintendent. Email not publicly listed — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3744,24 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>1412 W. Platte Ave., Fort Morgan, CO 80701</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
+          <t>1412 W. Platte Ave., Sterling, CO 80751</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Dustin</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="3" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr">
@@ -3535,7 +3779,7 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>Serves Sterling, CO area. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Dustin Hunt, Superintendent (recent appointment). Serves Sterling, CO area. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3568,9 +3812,21 @@
           <t>155 Panther Way, Woodland Park, CO 80863</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Slocum</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr">
@@ -3588,7 +3844,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Ginger Slocum named Superintendent effective July 1, 2026. Email not yet established — contact district office.</t>
         </is>
       </c>
     </row>
@@ -3694,9 +3950,21 @@
           <t>775 Yampa Ave., Craig, CO 81625</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Mathew</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Neal</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr">
@@ -3718,7 +3986,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>Creative Curriculum confirmed. ECE director name not confirmed; email needed — check Apollo.io.</t>
+          <t>Creative Curriculum confirmed. Mathew Neal, Ed.D., Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3751,9 +4019,21 @@
           <t>420 Birch St., Gilcrest, CO 80623</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Bloemen</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Interim Superintendent</t>
+        </is>
+      </c>
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="3" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr">
@@ -3775,7 +4055,7 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Kim Bloemen is Interim Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3808,9 +4088,21 @@
           <t>309 Lewis St., Pagosa Springs, CO 81147</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Holt</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="4" t="inlineStr">
@@ -3828,7 +4120,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Rick Holt, Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -3881,7 +4173,7 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>IB World School. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>IB World School. Superintendent name not found in public sources — contact district office directly at 970-925-3760.</t>
         </is>
       </c>
     </row>
@@ -3946,7 +4238,7 @@
       </c>
       <c r="Q55" s="4" t="inlineStr">
         <is>
-          <t>Name confirmed from official staff directory. Email needed — check Apollo.io.</t>
+          <t>Name confirmed from official staff directory. Email not found — check Apollo.io. Superintendent: Marsha Cody.</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4307,7 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>Head Start participant. Superintendent listed as primary contact for small district.</t>
+          <t>Head Start participant. Superintendent email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4048,9 +4340,21 @@
           <t>PO Box 368, Kersey, CO 80644</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Burmeister</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="4" t="inlineStr">
@@ -4068,7 +4372,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>Small district. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Jeremy Burmeister, Ed.D., Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4101,9 +4405,21 @@
           <t>0098 CR 233, Glenwood Springs, CO 81601</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Baugh</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="3" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr">
@@ -4121,7 +4437,7 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>Small rural district. ECE director name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Small rural district. Superintendent email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4502,7 @@
       </c>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Superintendent confirmed. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4567,7 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Superintendent confirmed. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4281,21 +4597,29 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>1505 Brodie Ave., Estes Park, CO 80517</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr"/>
+          <t>1605 Brodie Ave., Estes Park, CO 80517</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Bode</t>
+        </is>
+      </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Preschool Contact</t>
+          <t>Superintendent</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>970-586-8600</t>
+          <t>970-586-2361</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr"/>
@@ -4307,12 +4631,12 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>https://www.estesschools.org/in-our-schools/programs/preschool</t>
+          <t>https://www.estesschools.org/our-district/district-leadership/superintendent</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
         <is>
-          <t>Active UPK program. Preschool contact name not confirmed. Email needed — check Apollo.io.</t>
+          <t>Ruby Bode confirmed as Superintendent. Direct email not on website — contact admin assistant Christine Douglas (christine_douglas@estesschools.org) for appointment.</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4666,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>715 E. Main St., Buena Vista, CO 81211</t>
+          <t>113 North Court Street, Buena Vista, CO 81211</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4364,7 +4688,7 @@
       <c r="K62" s="3" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>719-395-8011</t>
+          <t>719-395-7005</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr"/>
@@ -4372,12 +4696,12 @@
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bvsd.k12.co.us</t>
+          <t>https://www.bvschools.org/staff</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>Note: do not confuse with Boulder Valley SD (also abbreviated BVSD). Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Note: do not confuse with Boulder Valley SD (also BVSD). Lisa Yates confirmed as Superintendent. Email not publicly listed — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4761,12 @@
       <c r="O63" s="4" t="inlineStr"/>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>https://www.la-schools.com</t>
+          <t>https://www.la-schools.com/staff</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Toby Melster confirmed as Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4796,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>400 S. Main St., Yuma, CO 80759</t>
+          <t>1115 South Ash Street, Yuma, CO 80759</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4490,11 +4814,19 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>jfraley@yumaschools.org</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>970-848-2265</t>
+          <t>970-848-5831</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr"/>
@@ -4502,12 +4834,12 @@
       <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>https://www.yumaschools.org</t>
+          <t>https://yumaschools.org/District/Staff/</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Jim Fraley confirmed as Superintendent. Email format estimated based on district pattern.</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4869,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>215 N. Animas St., Trinidad, CO 81082</t>
+          <t>607 Miner Drive, Trinidad, CO 81082</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -4559,7 +4891,7 @@
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>719-846-4400</t>
+          <t>719-846-3324</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr"/>
@@ -4567,12 +4899,12 @@
       <c r="O65" s="4" t="inlineStr"/>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>https://www.tsd1.org</t>
+          <t>https://www.tsd1.org/</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>Superintendent through July 2026; transition possible. Email needed — check Apollo.io.</t>
+          <t>Olivia Bachicha confirmed as Superintendent (through July 2026). Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4602,17 +4934,17 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>340 S. Lincoln St., Burlington, CO 80807</t>
+          <t>2600 Rose Ave., PO Box 369, Burlington, CO 80807</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Shane</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Satterly</t>
+          <t>Walkinshaw</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4624,7 +4956,7 @@
       <c r="K66" s="3" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>719-346-8521</t>
+          <t>719-346-8737</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr"/>
@@ -4632,12 +4964,12 @@
       <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>https://www.burl.k12.co.us</t>
+          <t>https://www.burlingtonk12.org/</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>Superintendent listed as primary contact. Email needed — check Apollo.io.</t>
+          <t>Shane Walkinshaw is current Superintendent (Tom Satterly was previous). Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4667,17 +4999,37 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>PO Box 1089, Meeker, CO 81641</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr"/>
-      <c r="K67" s="4" t="inlineStr"/>
+          <t>PO Box 1089, 555 Garfield, Meeker, CO 81641</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Selle</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>chris.selle@meeker.k12.co.us</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>970-878-9040</t>
+          <t>970-878-9050</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr"/>
@@ -4685,12 +5037,12 @@
       <c r="O67" s="4" t="inlineStr"/>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>https://www.meeker.k12.co.us</t>
+          <t>https://www.meeker.k12.co.us/contact-us</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>Small rural district. ECE contact not confirmed. Email needed — check Apollo.io.</t>
+          <t>Chris Selle confirmed as Superintendent with direct email and phone (ext. 102).</t>
         </is>
       </c>
     </row>
@@ -4720,17 +5072,29 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>PO Box 10, Idaho Springs, CO 80452</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="3" t="inlineStr"/>
+          <t>320 HWY 103, Idaho Springs, CO 80452</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Wes</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Paxton</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>303-567-4438</t>
+          <t>303-567-3850</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr"/>
@@ -4738,12 +5102,12 @@
       <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>https://www.clearcreek.k12.co.us</t>
+          <t>https://www.ccsdre1.org/en-US</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>Small mountain district. ECE contact not confirmed. Email needed — check Apollo.io.</t>
+          <t>Wes Paxton confirmed as Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4773,12 +5137,16 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>PO Box 97, Center, CO 81125</t>
+          <t>550 S. Sylvester Avenue, Center, CO 81125</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr"/>
       <c r="L69" s="4" t="inlineStr">
@@ -4791,12 +5159,12 @@
       <c r="O69" s="4" t="inlineStr"/>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>https://www.center.k12.co.us</t>
+          <t>https://www.center.k12.co.us/</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
         <is>
-          <t>Small rural district. ECE contact not confirmed. Email needed — check Apollo.io.</t>
+          <t>Current superintendent not found in public sources (previous: Carrie Zimmerman, 2019). Contact district office at 719-754-3442.</t>
         </is>
       </c>
     </row>
@@ -4826,17 +5194,21 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>PO Box 38, Bailey, CO 80421</t>
+          <t>Fairplay, CO 80440</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>303-838-5400</t>
+          <t>719-836-4401</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr"/>
@@ -4844,12 +5216,12 @@
       <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>https://www.parkre2.org</t>
+          <t>https://www.parkcountyre2.org/en-US/district-information-e2f3bea0</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>Small mountain district. ECE contact not confirmed. Email needed — check Apollo.io.</t>
+          <t>Superintendent name not found in public sources. Contact district office at 719-836-4401.</t>
         </is>
       </c>
     </row>
@@ -4879,17 +5251,29 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>701 N. 10th St., Rocky Ford, CO 81067</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr"/>
+          <t>601 South 8th Street, Rocky Ford, CO 81067</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Kermit</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Snyder</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>719-254-7435</t>
+          <t>719-254-7423</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr"/>
@@ -4897,12 +5281,12 @@
       <c r="O71" s="4" t="inlineStr"/>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>https://www.rockyford.k12.co.us</t>
+          <t>https://www.rockyfordk12.org/</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>Small rural district. ECE contact not confirmed. Email needed — check Apollo.io.</t>
+          <t>Kermit Snyder confirmed as Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -4932,12 +5316,16 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>PO Box 1, Rangely, CO 81648</t>
+          <t>402 West Main St., Rangely, CO 81648</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent (Vacancy)</t>
+        </is>
+      </c>
       <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="3" t="inlineStr"/>
       <c r="L72" s="3" t="inlineStr">
@@ -4950,12 +5338,12 @@
       <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>https://www.rangely.k12.co.us</t>
+          <t>https://www.rangelyk12.org/page/superintendent-message</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>Very small district. Superintendent is likely ECE contact. Email needed — check Apollo.io.</t>
+          <t>Superintendent vacancy as of 2025-26. District recruiting for July 1, 2026 start (search firm: McPherson &amp; Jacobson). Contact district office.</t>
         </is>
       </c>
     </row>
@@ -4990,7 +5378,11 @@
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr">
@@ -5003,12 +5395,12 @@
       <c r="O73" s="4" t="inlineStr"/>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>https://www.hayden.k12.co.us</t>
+          <t>https://www.haydenschools.org/</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
         <is>
-          <t>Very small district. Superintendent is likely ECE contact. Email needed — check Apollo.io.</t>
+          <t>Superintendent name not found in public sources. Contact district office at 970-276-3864.</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5430,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>115 W. 5th St., Walsenburg, CO 81089</t>
+          <t>201 East Fifth Street, Walsenburg, CO 81089</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5068,12 +5460,12 @@
       <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>https://www.huerfano.k12.co.us</t>
+          <t>https://huerfano.k12.co.us/en-US/superintendent</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>Also known as Bobby Howard. Small district. Email needed — check Apollo.io.</t>
+          <t>Also known as Bobby Howard. Superintendent confirmed. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -5106,14 +5498,26 @@
           <t>PO Box 99, Ordway, CO 81063</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>719-267-3521</t>
+          <t>719-267-3117</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr"/>
@@ -5121,12 +5525,12 @@
       <c r="O75" s="4" t="inlineStr"/>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>https://www.crowley.k12.co.us</t>
+          <t>https://www.cde.state.co.us/schoolview/explore/profile/0770</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>Very small district (&lt;320 students). Superintendent is ECE contact. Email needed — check Apollo.io.</t>
+          <t>Juan Ramirez confirmed as Superintendent per CDE. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5565,16 @@
       </c>
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="3" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>719-763-2367</t>
+          <t>970-522-7424</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr"/>
@@ -5174,12 +5582,12 @@
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>https://www.buffalo.k12.co.us</t>
+          <t>https://www.merinorams.com/</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>Very small district (&lt;310 students). Superintendent is ECE contact. Email needed — check Apollo.io.</t>
+          <t>Very small district. Superintendent name not found — contact district office. General district email: trampj@merinok12.com.</t>
         </is>
       </c>
     </row>
@@ -5212,14 +5620,26 @@
           <t>PO Box 97, Moffat, CO 81143</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Ande</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>719-256-4523</t>
+          <t>719-745-0500</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr"/>
@@ -5227,12 +5647,12 @@
       <c r="O77" s="4" t="inlineStr"/>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>https://www.moffat.k12.co.us</t>
+          <t>https://www.moffatschools.org/about-our-district/administration</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
         <is>
-          <t>Very small district (&lt;215 students). Superintendent is ECE contact. Email needed — check Apollo.io.</t>
+          <t>Ande Davis confirmed as Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -5265,9 +5685,21 @@
           <t>PO Box 38, Cheraw, CO 81030</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Snyder</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="3" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr">
@@ -5280,12 +5712,12 @@
       <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>https://www.cheraw.k12.co.us</t>
+          <t>https://cheraw.k12.co.us/en-US/our-superintendent-e4c3e15d</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>Very small district (~210 students). Superintendent is ECE contact. Email needed — check Apollo.io.</t>
+          <t>Matthew Snyder confirmed as Superintendent. Email not found — check Apollo.io.</t>
         </is>
       </c>
     </row>
